--- a/frontend/public/employee_directory.xlsx
+++ b/frontend/public/employee_directory.xlsx
@@ -24236,7 +24236,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>avi1997verma@gmail.com</t>
+          <t>Anirudh.verma@smartworlddevelopers.com</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
